--- a/src/app/modules/dashboard/excel_files/whole-food-plant-based-diet-chinese-and-japanese-noodle-recipes.xlsx
+++ b/src/app/modules/dashboard/excel_files/whole-food-plant-based-diet-chinese-and-japanese-noodle-recipes.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -10672,7 +10672,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -10780,7 +10780,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -12140,7 +12140,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -12150,7 +12150,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -12532,7 +12532,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -12728,7 +12728,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'noodles', 'stir-fry', 'soups', 'bowls', 'ethnic', 'asian']</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
